--- a/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20641,7 +20641,7 @@
         <v>0</v>
       </c>
       <c r="G470" t="n">
-        <v>0.4446</v>
+        <v>0.23707</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -20684,7 +20684,7 @@
         <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>0.45931</v>
+        <v>0.329413</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="G472" t="n">
-        <v>0.428312</v>
+        <v>0.338318</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -20770,7 +20770,7 @@
         <v>0</v>
       </c>
       <c r="G473" t="n">
-        <v>0.472327</v>
+        <v>0.416664</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -20810,10 +20810,10 @@
         <v>0.032112</v>
       </c>
       <c r="F474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>0.495655</v>
+        <v>0.684738</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -20853,10 +20853,10 @@
         <v>0.028567</v>
       </c>
       <c r="F475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G475" t="n">
-        <v>0.472815</v>
+        <v>0.53731</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -20896,10 +20896,10 @@
         <v>0.119043</v>
       </c>
       <c r="F476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G476" t="n">
-        <v>0.443021</v>
+        <v>0.53942</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -20942,7 +20942,7 @@
         <v>0</v>
       </c>
       <c r="G477" t="n">
-        <v>0.484954</v>
+        <v>0.300319</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20985,7 +20985,7 @@
         <v>0</v>
       </c>
       <c r="G478" t="n">
-        <v>0.454629</v>
+        <v>0.417742</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -21028,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0.553612</v>
+        <v>0.70378</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -21071,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0.5300859999999999</v>
+        <v>0.592262</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -21114,7 +21114,7 @@
         <v>1</v>
       </c>
       <c r="G481" t="n">
-        <v>0.550529</v>
+        <v>0.650674</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -21154,10 +21154,10 @@
         <v>0.072171</v>
       </c>
       <c r="F482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0.494842</v>
+        <v>0.715321</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -21197,10 +21197,10 @@
         <v>0.042677</v>
       </c>
       <c r="F483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0.465677</v>
+        <v>0.57904</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>0</v>
       </c>
       <c r="G484" t="n">
-        <v>0.463229</v>
+        <v>0.356512</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -21286,7 +21286,7 @@
         <v>0</v>
       </c>
       <c r="G485" t="n">
-        <v>0.463133</v>
+        <v>0.295368</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -21326,10 +21326,10 @@
         <v>0.303026</v>
       </c>
       <c r="F486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G486" t="n">
-        <v>0.463075</v>
+        <v>0.604472</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -21372,7 +21372,7 @@
         <v>0</v>
       </c>
       <c r="G487" t="n">
-        <v>0.482816</v>
+        <v>0.468918</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -21412,10 +21412,10 @@
         <v>0.593657</v>
       </c>
       <c r="F488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>0.448074</v>
+        <v>0.552593</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -21458,7 +21458,7 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0.520083</v>
+        <v>0.867156</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -21498,10 +21498,10 @@
         <v>0.011108</v>
       </c>
       <c r="F490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G490" t="n">
-        <v>0.46112</v>
+        <v>0.559706</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -21544,7 +21544,7 @@
         <v>0</v>
       </c>
       <c r="G491" t="n">
-        <v>0.432447</v>
+        <v>0.395539</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -21587,7 +21587,7 @@
         <v>0</v>
       </c>
       <c r="G492" t="n">
-        <v>0.46058</v>
+        <v>0.389335</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -21627,10 +21627,10 @@
         <v>0.143696</v>
       </c>
       <c r="F493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G493" t="n">
-        <v>0.484808</v>
+        <v>0.6180600000000001</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>0</v>
       </c>
       <c r="G494" t="n">
-        <v>0.398567</v>
+        <v>0.287193</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -21716,7 +21716,7 @@
         <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>0.437178</v>
+        <v>0.353425</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -21759,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="G496" t="n">
-        <v>0.464156</v>
+        <v>0.343316</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="G497" t="n">
-        <v>0.473631</v>
+        <v>0.259195</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -21845,7 +21845,7 @@
         <v>0</v>
       </c>
       <c r="G498" t="n">
-        <v>0.491734</v>
+        <v>0.463284</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -21888,7 +21888,7 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0.509178</v>
+        <v>0.685731</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -21931,7 +21931,7 @@
         <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0.523383</v>
+        <v>0.537162</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0.505123</v>
+        <v>0.504912</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -22014,10 +22014,10 @@
         <v>0.45441</v>
       </c>
       <c r="F502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0.490813</v>
+        <v>0.673476</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -22057,10 +22057,10 @@
         <v>0.07513</v>
       </c>
       <c r="F503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G503" t="n">
-        <v>0.4841</v>
+        <v>0.5782659999999999</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>0.44847</v>
+        <v>0.384431</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -22146,7 +22146,7 @@
         <v>0</v>
       </c>
       <c r="G505" t="n">
-        <v>0.471088</v>
+        <v>0.434547</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -22189,7 +22189,7 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0.5283060000000001</v>
+        <v>0.599285</v>
       </c>
       <c r="H506" t="n">
         <v>1</v>
@@ -22232,7 +22232,7 @@
         <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0.533085</v>
+        <v>0.60727</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="G508" t="n">
-        <v>0.403265</v>
+        <v>0.342061</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -22315,10 +22315,10 @@
         <v>0.734239</v>
       </c>
       <c r="F509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0.476964</v>
+        <v>0.583572</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -22361,7 +22361,7 @@
         <v>0</v>
       </c>
       <c r="G510" t="n">
-        <v>0.476992</v>
+        <v>0.388506</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="G511" t="n">
-        <v>0.416642</v>
+        <v>0.428292</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -22447,7 +22447,7 @@
         <v>0</v>
       </c>
       <c r="G512" t="n">
-        <v>0.473867</v>
+        <v>0.489703</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0.1593</v>
       </c>
       <c r="F513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0.472264</v>
+        <v>0.584712</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -22530,10 +22530,10 @@
         <v>0.796222</v>
       </c>
       <c r="F514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0.48801</v>
+        <v>0.647873</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -22573,10 +22573,10 @@
         <v>0.994285</v>
       </c>
       <c r="F515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0.485662</v>
+        <v>0.730564</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -22619,7 +22619,7 @@
         <v>0</v>
       </c>
       <c r="G516" t="n">
-        <v>0.474253</v>
+        <v>0.471336</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -22662,7 +22662,7 @@
         <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>0.454325</v>
+        <v>0.490766</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -22705,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="G518" t="n">
-        <v>0.401901</v>
+        <v>0.343302</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -22748,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="G519" t="n">
-        <v>0.428025</v>
+        <v>0.315611</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -22791,7 +22791,7 @@
         <v>0</v>
       </c>
       <c r="G520" t="n">
-        <v>0.417513</v>
+        <v>0.22303</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -22834,7 +22834,7 @@
         <v>0</v>
       </c>
       <c r="G521" t="n">
-        <v>0.397637</v>
+        <v>0.342662</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="G522" t="n">
-        <v>0.450041</v>
+        <v>0.336067</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>0</v>
       </c>
       <c r="G523" t="n">
-        <v>0.444086</v>
+        <v>0.426673</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -22963,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="G524" t="n">
-        <v>0.458545</v>
+        <v>0.257021</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -23006,7 +23006,7 @@
         <v>0</v>
       </c>
       <c r="G525" t="n">
-        <v>0.441578</v>
+        <v>0.443759</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
       <c r="G526" t="n">
-        <v>0.463634</v>
+        <v>0.305921</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="G527" t="n">
-        <v>0.426328</v>
+        <v>0.383606</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -23135,7 +23135,7 @@
         <v>0</v>
       </c>
       <c r="G528" t="n">
-        <v>0.451272</v>
+        <v>0.328335</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="G529" t="n">
-        <v>0.439422</v>
+        <v>0.316815</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>0</v>
       </c>
       <c r="G530" t="n">
-        <v>0.446045</v>
+        <v>0.384801</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -23264,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="G531" t="n">
-        <v>0.467226</v>
+        <v>0.473815</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="G532" t="n">
-        <v>0.411533</v>
+        <v>0.370863</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="G533" t="n">
-        <v>0.467138</v>
+        <v>0.379286</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>0</v>
       </c>
       <c r="G534" t="n">
-        <v>0.440276</v>
+        <v>0.334372</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -23436,7 +23436,7 @@
         <v>0</v>
       </c>
       <c r="G535" t="n">
-        <v>0.438697</v>
+        <v>0.327162</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -23479,7 +23479,7 @@
         <v>0</v>
       </c>
       <c r="G536" t="n">
-        <v>0.458979</v>
+        <v>0.43303</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -23522,7 +23522,7 @@
         <v>0</v>
       </c>
       <c r="G537" t="n">
-        <v>0.43339</v>
+        <v>0.415876</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -23565,7 +23565,7 @@
         <v>0</v>
       </c>
       <c r="G538" t="n">
-        <v>0.416415</v>
+        <v>0.26143</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="G539" t="n">
-        <v>0.429679</v>
+        <v>0.380432</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="G540" t="n">
-        <v>0.478583</v>
+        <v>0.369778</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0.501556</v>
+        <v>0.5599189999999999</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
       <c r="G542" t="n">
-        <v>0.494075</v>
+        <v>0.360332</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -23777,10 +23777,10 @@
         <v>0.011385</v>
       </c>
       <c r="F543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>0.501395</v>
+        <v>0.346518</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>0</v>
       </c>
       <c r="G544" t="n">
-        <v>0.475058</v>
+        <v>0.410555</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -23866,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="G545" t="n">
-        <v>0.468537</v>
+        <v>0.378982</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>0.39733</v>
+        <v>0.364417</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="G547" t="n">
-        <v>0.442459</v>
+        <v>0.327856</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -23995,7 +23995,7 @@
         <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>0.44587</v>
+        <v>0.432341</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -24038,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="G549" t="n">
-        <v>0.466938</v>
+        <v>0.448004</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -24081,7 +24081,7 @@
         <v>0</v>
       </c>
       <c r="G550" t="n">
-        <v>0.454177</v>
+        <v>0.32075</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -24124,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="G551" t="n">
-        <v>0.460001</v>
+        <v>0.345081</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -24167,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="G552" t="n">
-        <v>0.454533</v>
+        <v>0.309911</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -24210,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="G553" t="n">
-        <v>0.498466</v>
+        <v>0.389368</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -24253,7 +24253,7 @@
         <v>0</v>
       </c>
       <c r="G554" t="n">
-        <v>0.484624</v>
+        <v>0.406823</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="G555" t="n">
-        <v>0.489831</v>
+        <v>0.402189</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="G556" t="n">
-        <v>0.4396</v>
+        <v>0.426751</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -24379,10 +24379,10 @@
         <v>0.060583</v>
       </c>
       <c r="F557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G557" t="n">
-        <v>0.498813</v>
+        <v>0.555525</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -24425,7 +24425,7 @@
         <v>0</v>
       </c>
       <c r="G558" t="n">
-        <v>0.440738</v>
+        <v>0.345822</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="G559" t="n">
-        <v>0.473315</v>
+        <v>0.450473</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="G560" t="n">
-        <v>0.477181</v>
+        <v>0.402502</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -24551,10 +24551,10 @@
         <v>0.017566</v>
       </c>
       <c r="F561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G561" t="n">
-        <v>0.509395</v>
+        <v>0.40624</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -24594,10 +24594,10 @@
         <v>0.036399</v>
       </c>
       <c r="F562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G562" t="n">
-        <v>0.527941</v>
+        <v>0.439556</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -24640,7 +24640,7 @@
         <v>1</v>
       </c>
       <c r="G563" t="n">
-        <v>0.530092</v>
+        <v>0.543766</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -24683,7 +24683,7 @@
         <v>0</v>
       </c>
       <c r="G564" t="n">
-        <v>0.468476</v>
+        <v>0.296998</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -24726,7 +24726,7 @@
         <v>0</v>
       </c>
       <c r="G565" t="n">
-        <v>0.483287</v>
+        <v>0.426855</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -24769,7 +24769,7 @@
         <v>0</v>
       </c>
       <c r="G566" t="n">
-        <v>0.492396</v>
+        <v>0.381403</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="G567" t="n">
-        <v>0.466518</v>
+        <v>0.26135</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -24855,7 +24855,7 @@
         <v>0</v>
       </c>
       <c r="G568" t="n">
-        <v>0.446911</v>
+        <v>0.36909</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -24898,7 +24898,7 @@
         <v>0</v>
       </c>
       <c r="G569" t="n">
-        <v>0.489825</v>
+        <v>0.427867</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
         <v>0</v>
       </c>
       <c r="G570" t="n">
-        <v>0.486984</v>
+        <v>0.372153</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
         <v>0</v>
       </c>
       <c r="G571" t="n">
-        <v>0.475993</v>
+        <v>0.393626</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -25027,7 +25027,7 @@
         <v>0</v>
       </c>
       <c r="G572" t="n">
-        <v>0.49303</v>
+        <v>0.398641</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="G573" t="n">
-        <v>0.449188</v>
+        <v>0.26851</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -25113,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="G574" t="n">
-        <v>0.46582</v>
+        <v>0.409207</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="G575" t="n">
-        <v>0.467205</v>
+        <v>0.2867</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -25199,7 +25199,7 @@
         <v>0</v>
       </c>
       <c r="G576" t="n">
-        <v>0.449555</v>
+        <v>0.393304</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -25242,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="G577" t="n">
-        <v>0.449485</v>
+        <v>0.459684</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="G578" t="n">
-        <v>0.477289</v>
+        <v>0.46374</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -25325,10 +25325,10 @@
         <v>0.257352</v>
       </c>
       <c r="F579" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0.498208</v>
+        <v>0.511266</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G580" t="n">
-        <v>0.473408</v>
+        <v>0.432112</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -25414,7 +25414,7 @@
         <v>0</v>
       </c>
       <c r="G581" t="n">
-        <v>0.462744</v>
+        <v>0.490701</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -25457,7 +25457,7 @@
         <v>0</v>
       </c>
       <c r="G582" t="n">
-        <v>0.462842</v>
+        <v>0.38983</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="G583" t="n">
-        <v>0.423699</v>
+        <v>0.411755</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -25540,10 +25540,10 @@
         <v>0.010808</v>
       </c>
       <c r="F584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G584" t="n">
-        <v>0.511459</v>
+        <v>0.422083</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="G585" t="n">
-        <v>0.481476</v>
+        <v>0.418079</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -25629,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="G586" t="n">
-        <v>0.423742</v>
+        <v>0.26733</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         <v>0</v>
       </c>
       <c r="G587" t="n">
-        <v>0.49211</v>
+        <v>0.429041</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="G588" t="n">
-        <v>0.433997</v>
+        <v>0.294489</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -25755,10 +25755,10 @@
         <v>0.021812</v>
       </c>
       <c r="F589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G589" t="n">
-        <v>0.489582</v>
+        <v>0.500381</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -25801,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="G590" t="n">
-        <v>0.479212</v>
+        <v>0.430589</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -25844,7 +25844,7 @@
         <v>0</v>
       </c>
       <c r="G591" t="n">
-        <v>0.461503</v>
+        <v>0.410652</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -25884,10 +25884,10 @@
         <v>0.056458</v>
       </c>
       <c r="F592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G592" t="n">
-        <v>0.472275</v>
+        <v>0.530985</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0.123358</v>
       </c>
       <c r="F593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G593" t="n">
-        <v>0.510377</v>
+        <v>0.426764</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -25970,10 +25970,10 @@
         <v>0.026617</v>
       </c>
       <c r="F594" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G594" t="n">
-        <v>0.510231</v>
+        <v>0.35726</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -26016,7 +26016,7 @@
         <v>0</v>
       </c>
       <c r="G595" t="n">
-        <v>0.482639</v>
+        <v>0.440015</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>0</v>
       </c>
       <c r="G596" t="n">
-        <v>0.441756</v>
+        <v>0.399586</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>0</v>
       </c>
       <c r="G597" t="n">
-        <v>0.497463</v>
+        <v>0.35805</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -26145,7 +26145,7 @@
         <v>0</v>
       </c>
       <c r="G598" t="n">
-        <v>0.490656</v>
+        <v>0.444678</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -26188,7 +26188,7 @@
         <v>1</v>
       </c>
       <c r="G599" t="n">
-        <v>0.556014</v>
+        <v>0.668622</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -26231,7 +26231,7 @@
         <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>0.523474</v>
+        <v>0.6039949999999999</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -26274,7 +26274,7 @@
         <v>0</v>
       </c>
       <c r="G601" t="n">
-        <v>0.482416</v>
+        <v>0.357053</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>0</v>
       </c>
       <c r="G602" t="n">
-        <v>0.453915</v>
+        <v>0.399306</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="G603" t="n">
-        <v>0.484766</v>
+        <v>0.419251</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="G604" t="n">
-        <v>0.477695</v>
+        <v>0.232456</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
         <v>0</v>
       </c>
       <c r="G605" t="n">
-        <v>0.453893</v>
+        <v>0.338616</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -26489,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="G606" t="n">
-        <v>0.456018</v>
+        <v>0.271929</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -26532,7 +26532,7 @@
         <v>0</v>
       </c>
       <c r="G607" t="n">
-        <v>0.456719</v>
+        <v>0.383579</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -26575,7 +26575,7 @@
         <v>0</v>
       </c>
       <c r="G608" t="n">
-        <v>0.465283</v>
+        <v>0.321141</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -26615,10 +26615,10 @@
         <v>0.34476</v>
       </c>
       <c r="F609" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G609" t="n">
-        <v>0.446742</v>
+        <v>0.584562</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -26661,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="G610" t="n">
-        <v>0.461833</v>
+        <v>0.341907</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -26701,10 +26701,10 @@
         <v>0.020912</v>
       </c>
       <c r="F611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G611" t="n">
-        <v>0.489744</v>
+        <v>0.580777</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -26747,7 +26747,7 @@
         <v>0</v>
       </c>
       <c r="G612" t="n">
-        <v>0.420387</v>
+        <v>0.282425</v>
       </c>
       <c r="H612" t="n">
         <v>0</v>
@@ -26787,10 +26787,10 @@
         <v>0.136831</v>
       </c>
       <c r="F613" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G613" t="n">
-        <v>0.5020829999999999</v>
+        <v>0.413916</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>0</v>
       </c>
       <c r="G614" t="n">
-        <v>0.459674</v>
+        <v>0.288595</v>
       </c>
       <c r="H614" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="G615" t="n">
-        <v>0.451222</v>
+        <v>0.237059</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -26916,10 +26916,10 @@
         <v>0.007229</v>
       </c>
       <c r="F616" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G616" t="n">
-        <v>0.507786</v>
+        <v>0.44398</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="G617" t="n">
-        <v>0.418322</v>
+        <v>0.344316</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -27002,10 +27002,10 @@
         <v>0.006522</v>
       </c>
       <c r="F618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>0.517637</v>
+        <v>0.384485</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -27048,7 +27048,7 @@
         <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>0.454657</v>
+        <v>0.335056</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -27091,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="G620" t="n">
-        <v>0.483892</v>
+        <v>0.315779</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -27134,7 +27134,7 @@
         <v>0</v>
       </c>
       <c r="G621" t="n">
-        <v>0.474781</v>
+        <v>0.373331</v>
       </c>
       <c r="H621" t="n">
         <v>0</v>
@@ -27174,10 +27174,10 @@
         <v>0.009244</v>
       </c>
       <c r="F622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>0.452104</v>
+        <v>0.515221</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -27220,7 +27220,7 @@
         <v>0</v>
       </c>
       <c r="G623" t="n">
-        <v>0.423868</v>
+        <v>0.361996</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
